--- a/survey_templates/039_regional_rural_banks_branding_quiz--survey_templates.xlsx
+++ b/survey_templates/039_regional_rural_banks_branding_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>regional_rural_banks_branding_quiz_form</t>
+          <t>branding_knowledge</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>regional_rural_banks_branding_quiz</t>
+          <t>What is the name of our regional bank?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>branding_knowledge_test</t>
+          <t>logo_recognition</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>branding_knowledge</t>
+          <t>Which of the following logos are recognized as our regional bank?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>recognition_test</t>
+          <t>years_of_familiarity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>recognition</t>
+          <t>How many years have you been familiar with our regional bank?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>familiarity_test</t>
+          <t>age_group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>familiarity</t>
+          <t>What is your age group?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>quiz_score</t>
+          <t>expected_score</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>quiz_score</t>
+          <t>What is the score you think you would get out of 100 if you were to take the test?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>quiz_score_out_of</t>
+          <t>knowledge_of_history</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>quiz_score_out_of</t>
+          <t>How do you rate your knowledge of our regional bank's history?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>quiz_submission_date</t>
+          <t>relationship_with_bank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>quiz_submission_date</t>
+          <t>Which of the following describes your relationship with our regional bank?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>quiz_submission_time</t>
+          <t>service_offered</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>quiz_submission_time</t>
+          <t>Which of the following services does our regional bank offer?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>quiz_submission_comments</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>quiz_submission_comments</t>
+          <t>What are your comments about our regional bank?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
+          <t>quiz_submission</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
+          <t>What is your score out of 100?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -761,329 +761,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>regional_rural_banks_branding_quiz_form_submitted</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,51 +804,493 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>branding_knowledge_test_choices</t>
+          <t>logo_recognition_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>our_logo_with_a_red_and_blue_color_scheme</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option 1</t>
+          <t>Our logo with a red and blue color scheme</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>branding_knowledge_test_choices</t>
+          <t>logo_recognition_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>our_logo_with_a_green_and_yellow_color_scheme</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option 2</t>
+          <t>Our logo with a green and yellow color scheme</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>branding_knowledge_test_choices</t>
+          <t>years_of_familiarity_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>1_year</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1 year</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>years_of_familiarity_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2-5_years</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2-5 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>years_of_familiarity_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>more_than_5_years</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>More than 5 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>age_group_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>18-25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>18-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>age_group_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>26-35</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>26-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>age_group_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>36-45</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>36-45</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>age_group_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>46-55</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>46-55</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>age_group_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>56_and_above</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>56 and above</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>expected_score_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>less_than_30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Less than 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>expected_score_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>30-50</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>30-50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>expected_score_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>51-70</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>51-70</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>expected_score_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>71-90</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>71-90</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>expected_score_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>more_than_90</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>More than 90</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>knowledge_of_history_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>very_high</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Very high</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>knowledge_of_history_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>knowledge_of_history_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>knowledge_of_history_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>knowledge_of_history_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>very_low</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Very low</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>relationship_with_bank_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Very satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>relationship_with_bank_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>satisfied</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>relationship_with_bank_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>relationship_with_bank_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>dissatisfied</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>relationship_with_bank_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>very_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Very dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>service_offered_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>service_offered_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>service_offered_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>option_3</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>option 3</t>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>service_offered_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
